--- a/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103857</t>
+    <t>20250611134353</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:57+01:00</t>
+    <t>2025-06-11T13:43:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250611134353</t>
+    <t>20250616134740</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T13:43:53+01:00</t>
+    <t>2025-06-16T13:47:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134740</t>
+    <t>20250624152100</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:40+01:00</t>
+    <t>2025-06-24T15:21:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152100</t>
+    <t>20251028115834</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:00+01:00</t>
+    <t>2025-10-28T11:58:34+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251028115834</t>
+    <t>20251216141839</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T11:58:34+01:00</t>
+    <t>2025-12-16T14:18:39+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141839</t>
+    <t>20260220142104</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:39+01:00</t>
+    <t>2026-02-20T14:21:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142104</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:04+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-nihss-champ-visuel-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150250</t>
+    <t>20260619134042</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:50+01:00</t>
+    <t>2026-06-19T13:40:42+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
